--- a/reports/pdf_change_20260814.xlsx
+++ b/reports/pdf_change_20260814.xlsx
@@ -38,11 +38,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="11"/>
     </font>
@@ -67,6 +62,11 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -74,11 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -103,6 +98,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -143,19 +143,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,17 +170,12 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -540,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -566,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 2/7  ·  대기: KoAct, KoAct, TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,744억   ·   현금 130억(2.7%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 2종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -587,377 +588,1077 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>하나머티리얼즈</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>2853840000</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>1.40%→1.93%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>98→144</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>-450410400</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>0.21%→0.10%</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>36→18</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>1339030000</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>2.76%→3.12%</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>49→54</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-15</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>-956967000</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>0.75%→0.55%</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>55→40</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>-1305321600</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>4.09%→3.66%</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>168→156</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>-882208800</v>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>0.86%→0.66%</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>40→31</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>-396539000</v>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>0.32%→0.26%</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>20→15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,037억   ·   현금 10억(0.3%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,731억   ·   현금 31억(1.1%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 9종목  /  매도 7종목</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>PS일렉트로닉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>1178496000</v>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.44%</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>0→150</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>미코</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-271</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>-3720288000</v>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>2.66%→1.27%</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>521→250</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>미래에셋벤처투자</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>124</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>1533790720</v>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>0.54%→1.14%</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>126→250</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>네패스</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n">
+        <v>-230</v>
+      </c>
+      <c r="I19" s="15" t="n">
+        <v>-2948563200</v>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>1.21%→0.09%</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>250→20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>한국피아이엠  (신규)</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>3548160000</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.31%</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>0→80</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>메쥬</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-77</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>-696572800</v>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>0.34%→0.08%</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>101→24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>에스피지</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>1579776000</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>2.97%→3.50%</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>100→120</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>씨어스  (편출)</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-70</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>-1251712000</v>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>0.47%→0.00%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>70→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>티에스이  (신규)</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>3646720000</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.35%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>0→20</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-2962432000</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>2.00%→0.82%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>70→30</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>2756160000</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>1.64%→2.71%</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>25→40</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>케어젠  (편출)</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>-1088102400</v>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>0.41%→0.00%</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>24→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>43718400</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>0.58%→0.60%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>218→224</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-1640953600</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>5.66%→5.13%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>123→110</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>티엘비</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>65894400</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>0.94%→0.99%</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>119→122</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="n"/>
+      <c r="H25" s="17" t="n"/>
+      <c r="I25" s="17" t="n"/>
+      <c r="J25" s="17" t="n"/>
+      <c r="K25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>67795200</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>1.29%→1.28%</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>150→153</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="17" t="n"/>
+      <c r="J26" s="17" t="n"/>
+      <c r="K26" s="17" t="n"/>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,349억   ·   현금 22억(1.0%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 294억   ·   현금 7억(2.5%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="G32" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="8" t="n"/>
+      <c r="J32" s="8" t="n"/>
+      <c r="K32" s="8" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D33" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E33" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G33" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>코스맥스엔비티</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B34" s="11" t="n">
         <v>86</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C34" s="11" t="n">
         <v>65752160</v>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>0.10%→0.33%</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>36→122</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>더블유씨피</t>
         </is>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H34" s="15" t="n">
         <v>-82</v>
       </c>
-      <c r="I14" s="17" t="n">
+      <c r="I34" s="15" t="n">
         <v>-56212640</v>
       </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="J34" s="16" t="inlineStr">
         <is>
           <t>7.50%→7.30%</t>
         </is>
       </c>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="K34" s="13" t="inlineStr">
         <is>
           <t>3,134→3,052</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>서진시스템</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B35" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C35" s="11" t="n">
         <v>93423000</v>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>7.38%→7.70%</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>747→780</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G35" s="14" t="inlineStr">
         <is>
           <t>씨어스</t>
         </is>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H35" s="15" t="n">
         <v>-43</v>
       </c>
-      <c r="I15" s="17" t="n">
+      <c r="I35" s="15" t="n">
         <v>-83007200</v>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="J35" s="16" t="inlineStr">
         <is>
           <t>6.87%→6.58%</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="K35" s="13" t="inlineStr">
         <is>
           <t>1,020→977</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
         <is>
           <t>한선엔지니어링</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B36" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C36" s="11" t="n">
         <v>31786240</v>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>1.53%→1.64%</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>442→474</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G36" s="14" t="inlineStr">
         <is>
           <t>스피어</t>
         </is>
       </c>
-      <c r="H16" s="17" t="n">
+      <c r="H36" s="15" t="n">
         <v>-34</v>
       </c>
-      <c r="I16" s="17" t="n">
+      <c r="I36" s="15" t="n">
         <v>-68734400</v>
       </c>
-      <c r="J16" s="18" t="inlineStr">
+      <c r="J36" s="16" t="inlineStr">
         <is>
           <t>2.80%→2.56%</t>
         </is>
       </c>
-      <c r="K16" s="15" t="inlineStr">
+      <c r="K36" s="13" t="inlineStr">
         <is>
           <t>397→363</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>노바렉스</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B37" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C37" s="11" t="n">
         <v>34624840</v>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>0.09%→0.21%</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>22→51</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>클래시스</t>
         </is>
       </c>
-      <c r="H17" s="17" t="n">
+      <c r="H37" s="15" t="n">
         <v>-8</v>
       </c>
-      <c r="I17" s="17" t="n">
+      <c r="I37" s="15" t="n">
         <v>-26630400</v>
       </c>
-      <c r="J17" s="18" t="inlineStr">
+      <c r="J37" s="16" t="inlineStr">
         <is>
           <t>0.65%→0.56%</t>
         </is>
       </c>
-      <c r="K17" s="15" t="inlineStr">
+      <c r="K37" s="13" t="inlineStr">
         <is>
           <t>56→48</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 596억   ·   현금 10억(1.7%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="20" t="n"/>
+      <c r="I42" s="20" t="n"/>
+      <c r="J42" s="20" t="n"/>
+      <c r="K42" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="18">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:K12"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="G16:K16"/>
+    <mergeCell ref="G32:K32"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A13:K13"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A40:K40"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260814.xlsx
+++ b/reports/pdf_change_20260814.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,744억   ·   현금 130억(2.7%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 2종목  /  매도 5종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,802억   ·   현금 131억(2.7%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 2종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>46</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2853840000</v>
+        <v>2867640000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-18</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-450410400</v>
+        <v>-452588400</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1339030000</v>
+        <v>1345505000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-15</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-956967000</v>
+        <v>-961594500</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         <v>-12</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1305321600</v>
+        <v>-1311633600</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>-9</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-882208800</v>
+        <v>-886474800</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>-5</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-396539000</v>
+        <v>-398456500</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,037억   ·   현금 10억(0.3%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,051억   ·   현금 10억(0.3%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -859,7 +859,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,731억   ·   현금 31억(1.1%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 9종목  /  매도 7종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,797억   ·   현금 32억(1.1%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 9종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -955,7 +955,7 @@
         <v>150</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1178496000</v>
+        <v>1195236000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>-271</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-3720288000</v>
+        <v>-3773133000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>124</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>1533790720</v>
+        <v>1555577520</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>-230</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-2948563200</v>
+        <v>-2990446200</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>80</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>3548160000</v>
+        <v>3598560000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>-77</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-696572800</v>
+        <v>-706467300</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1579776000</v>
+        <v>1602216000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>-70</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1251712000</v>
+        <v>-1269492000</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>3646720000</v>
+        <v>3698520000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>-40</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-2962432000</v>
+        <v>-3004512000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>15</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>2756160000</v>
+        <v>2795310000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>-24</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1088102400</v>
+        <v>-1103558400</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>6</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>43718400</v>
+        <v>44339400</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>-13</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1640953600</v>
+        <v>-1664262600</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>65894400</v>
+        <v>66830400</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>67795200</v>
+        <v>68758200</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,349억   ·   현금 22억(1.0%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,353억   ·   현금 23억(1.0%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1336,7 +1336,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 294억   ·   현금 7억(2.5%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 4종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 295억   ·   현금 7억(2.5%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1432,11 +1432,11 @@
         <v>86</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>65752160</v>
+        <v>63987440</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>0.10%→0.33%</t>
+          <t>0.09%→0.32%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -1453,11 +1453,11 @@
         <v>-82</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-56212640</v>
+        <v>-57708320</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>7.50%→7.30%</t>
+          <t>7.68%→7.47%</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
@@ -1476,11 +1476,11 @@
         <v>33</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>93423000</v>
+        <v>92670600</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>7.38%→7.70%</t>
+          <t>7.30%→7.62%</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -1497,11 +1497,11 @@
         <v>-43</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-83007200</v>
+        <v>-79085600</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>6.87%→6.58%</t>
+          <t>6.53%→6.25%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
@@ -1520,11 +1520,11 @@
         <v>32</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>31786240</v>
+        <v>34242560</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>1.53%→1.64%</t>
+          <t>1.65%→1.76%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -1541,11 +1541,11 @@
         <v>-34</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-68734400</v>
+        <v>-67054800</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>2.80%→2.56%</t>
+          <t>2.73%→2.49%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
@@ -1564,11 +1564,11 @@
         <v>29</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>34624840</v>
+        <v>33236320</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>0.09%→0.21%</t>
+          <t>0.09%→0.20%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -1585,11 +1585,11 @@
         <v>-8</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-26630400</v>
+        <v>-24137600</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.56%</t>
+          <t>0.59%→0.50%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -1601,7 +1601,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 596억   ·   현금 10억(1.7%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 602억   ·   현금 10억(1.7%)      당일 2026-08-14  vs  전영업일 2026-08-13      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>

--- a/reports/pdf_change_20260814.xlsx
+++ b/reports/pdf_change_20260814.xlsx
@@ -1080,23 +1080,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>티에스이  (신규)</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1602216000</v>
+        <v>3698520000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.97%→3.50%</t>
+          <t>0.00%→1.35%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>100→120</t>
+          <t>0→20</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1124,23 +1124,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>티에스이  (신규)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>3698520000</v>
+        <v>1602216000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.35%</t>
+          <t>2.97%→3.50%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>0→20</t>
+          <t>100→120</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">

--- a/reports/pdf_change_20260814.xlsx
+++ b/reports/pdf_change_20260814.xlsx
@@ -1080,23 +1080,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>티에스이  (신규)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3698520000</v>
+        <v>1602216000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.35%</t>
+          <t>2.97%→3.50%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>0→20</t>
+          <t>100→120</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1124,23 +1124,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>티에스이  (신규)</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1602216000</v>
+        <v>3698520000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.97%→3.50%</t>
+          <t>0.00%→1.35%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>100→120</t>
+          <t>0→20</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1256,23 +1256,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>66830400</v>
+        <v>68758200</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>0.94%→0.99%</t>
+          <t>1.29%→1.28%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>119→122</t>
+          <t>150→153</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -1284,23 +1284,23 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>68758200</v>
+        <v>66830400</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>1.29%→1.28%</t>
+          <t>0.94%→0.99%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>150→153</t>
+          <t>119→122</t>
         </is>
       </c>
       <c r="G26" s="17" t="n"/>

--- a/reports/pdf_change_20260814.xlsx
+++ b/reports/pdf_change_20260814.xlsx
@@ -1256,23 +1256,23 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>68758200</v>
+        <v>66830400</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>1.29%→1.28%</t>
+          <t>0.94%→0.99%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>150→153</t>
+          <t>119→122</t>
         </is>
       </c>
       <c r="G25" s="17" t="n"/>
@@ -1284,23 +1284,23 @@
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>66830400</v>
+        <v>68758200</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>0.94%→0.99%</t>
+          <t>1.29%→1.28%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>119→122</t>
+          <t>150→153</t>
         </is>
       </c>
       <c r="G26" s="17" t="n"/>
